--- a/docs/QC_KICH_BAN_KIEM_THU.xlsx
+++ b/docs/QC_KICH_BAN_KIEM_THU.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Luồng E2E &amp; Chuẩn bị" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Test cases" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Ma trận quyền" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Luong moi - Thu quy" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Test cases'!$A$1:$J$64</definedName>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,8 +70,12 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -92,8 +97,13 @@
         <fgColor rgb="00E7F0FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -115,11 +125,25 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -153,6 +177,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3641,4 +3671,1010 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Nhóm nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Vai trò</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>Màn hình</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Tiền điều kiện</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>Các bước thực hiện</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>Kết quả mong đợi</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>TC-N01</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Cấu trúc menu</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Mọi vai trò</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Drawer (menu)</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Đã đăng nhập</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Mở menu, xem nhóm "Thao tác"</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Các đầu mục có ĐÁNH SỐ 1,2,3…; Tài khoản &amp; Tin nhắn ở trên cùng; Hướng dẫn &amp; Đề xuất cải tiến ở cuối; KHÔNG còn mục Tất toán</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr"/>
+      <c r="I2" s="13" t="inlineStr"/>
+      <c r="J2" s="13" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>TC-N02</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Cấu trúc menu</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Mọi vai trò</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Drawer</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Đối chiếu tên các mục</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Đúng tên: Báo giá vật tư / Đề xuất mua hàng &amp; tạm ứng / Theo dõi đề xuất mua hàng &amp; tạm ứng / Duyệt đề xuất mua hàng / Nghiệm thu đơn hàng / Duyệt hồ sơ thanh toán / Đề xuất thanh toán / Duyệt đề xuất thanh toán / Theo dõi công nợ</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr"/>
+      <c r="I3" s="13" t="inlineStr"/>
+      <c r="J3" s="13" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>TC-N03</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Nghiệm thu</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Mua hàng</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Nghiệm thu đơn hàng</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Có khoản đã duyệt chờ nghiệm thu</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Nhập SL thực nhận, BỎ TRỐNG hạn TT / hóa đơn VAT / BBGN, bấm Lưu</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Bị chặn, báo thiếu từng mục bắt buộc (hạn TT, hóa đơn VAT, BBGN/phiếu cân/ảnh)</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr"/>
+      <c r="I4" s="13" t="inlineStr"/>
+      <c r="J4" s="13" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>TC-N04</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Nghiệm thu</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Mua hàng</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Nghiệm thu đơn hàng</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Nhập đủ SL + hạn TT + đính kèm VAT + đính kèm BBGN, Lưu</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Lưu thành công, gửi kế toán duyệt hồ sơ; kế toán nhận thông báo có mặt hàng + tổng tiền + người đề nghị</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr"/>
+      <c r="I5" s="13" t="inlineStr"/>
+      <c r="J5" s="13" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>TC-N05</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Duyệt hồ sơ TT</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Kế toán (KTTH)</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Duyệt hồ sơ thanh toán</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Có đơn đã nghiệm thu (chạy dummy_ktth_test.sql)</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Xem 1 đơn, kiểm chứng từ, nhập số đã trả trước (nếu có), bấm Lưu về công nợ</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Khoản chuyển sang "đã lưu công nợ" và biến mất khỏi danh sách chờ; xuất hiện ở Theo dõi công nợ</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr"/>
+      <c r="I6" s="13" t="inlineStr"/>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>Test lần lượt từng bộ phận</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>TC-N06</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Duyệt hồ sơ TT</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Kế toán</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Duyệt hồ sơ thanh toán</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Bấm "Trả lại NVMH bổ sung", nhập lý do</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>NVMH nhận thông báo trả lại; đơn quay lại danh sách nghiệm thu của NVMH (cần bổ sung)</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>TC-N07</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Duyệt hồ sơ TT</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Kế toán</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Duyệt hồ sơ thanh toán</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Bấm "💬 Nhắn tin NVMH" trên 1 hồ sơ</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Chuyển tới màn Tin nhắn, có gắn (dẫn chiếu) đúng mã phiếu của hồ sơ đó</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>TC-N08</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Đề xuất TT</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Kế toán</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Đề xuất thanh toán</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Có khoản đã lưu công nợ (dummy)</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Bấm "Nạp phiếu đã lưu công nợ (đến hạn)"</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Chỉ hiện khoản đã lưu công nợ; KHÔNG hiện khoản đang nằm trong ĐXTT chờ/đã duyệt</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr"/>
+      <c r="J9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>TC-N09</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Đề xuất TT</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Kế toán</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Đề xuất thanh toán</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Thêm 1 dòng tự nhập (khoản ngoài phần mềm) + giải trình, Gửi duyệt</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Tạo ĐXTT chờ duyệt; Chủ tịch nhận thông báo kèm tổng tiền + người lập</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr"/>
+      <c r="J10" s="13" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>TC-N10</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Đề xuất TT</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Kế toán</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Đề xuất thanh toán</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Xem mục "Đề xuất của tôi"</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Thấy ĐXTT đang trình / đã duyệt; phiếu Đã duyệt hiển thị "Chờ thủ quỹ chi" (KTTH không còn nút đi tiền)</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr"/>
+      <c r="I11" s="13" t="inlineStr"/>
+      <c r="J11" s="13" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>TC-N11</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Duyệt ĐXTT</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Chủ tịch</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Duyệt đề xuất thanh toán</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Có ĐXTT chờ duyệt (dummy)</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Duyệt gộp theo ngày</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Tất cả ĐXTT trong ngày chuyển Đã duyệt; kế toán/người lập nhận thông báo</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr"/>
+      <c r="J12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TC-N12</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Thủ quỹ</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Thủ quỹ</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Chi tiền (thủ quỹ)</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>ĐXTT đã Chủ tịch duyệt</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Mở màn, xem 1 phiếu</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Mỗi KHOẢN hiện đủ: số tiền · STK · ngân hàng · MST · mã CN · chứng từ; mỗi khoản có nút xác nhận + ô ảnh riêng</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr"/>
+      <c r="I13" s="13" t="inlineStr"/>
+      <c r="J13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>TC-N13</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Thủ quỹ</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Thủ quỹ</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Chi tiền (thủ quỹ)</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Chọn 1 khoản, BỎ TRỐNG ảnh, bấm xác nhận</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Bị chặn: bắt buộc đính kèm ảnh chuyển khoản</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr"/>
+      <c r="I14" s="13" t="inlineStr"/>
+      <c r="J14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>TC-N14</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Thủ quỹ</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Thủ quỹ</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Chi tiền (thủ quỹ)</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Đính kèm ảnh, xác nhận đã chuyển 1 khoản</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Khoản đó: công nợ tự trừ; hiện badge ✔ + ảnh; NVMH nhận thông báo "đã chuyển" khoản đó</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr"/>
+      <c r="J15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>TC-N15</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Thủ quỹ</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Thủ quỹ</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Chi tiền (thủ quỹ)</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Phiếu có nhiều khoản</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Xác nhận LẦN LƯỢT tất cả khoản của 1 phiếu</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Khi khoản cuối được xác nhận, phiếu tự chuyển "Đã chi" và rời khỏi hàng đợi</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TC-N16</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>NVMH xem ảnh</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Mua hàng</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Đề xuất mua hàng &amp; tạm ứng → Đề xuất của tôi</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Khoản của NVMH đã được thủ quỹ chi</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Mở "Đề xuất của tôi", xem phiếu tương ứng</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Hiện "✔ Đã chuyển tiền — Ảnh chuyển khoản: [link]"; mở xem được ảnh</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr"/>
+      <c r="I17" s="13" t="inlineStr"/>
+      <c r="J17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>TC-N17</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Chủ tịch / TGĐ / Kế toán</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Tổng quan điều hành</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>Có dữ liệu chi (sau khi thủ quỹ chi)</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Chọn khoảng ngày, Cập nhật</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Hiện: ĐXMH hôm nay (theo bộ phận), ĐXTT hôm nay, tổng chi trong kỳ theo bộ phận, chi tiết khoản đã chi (kèm ảnh), top NCC + lũy kế</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr"/>
+      <c r="I18" s="13" t="inlineStr"/>
+      <c r="J18" s="13" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TC-N18</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Công nợ thủ công</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Kế toán</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Cập nhật thanh toán (thủ công)</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Mở màn</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Hiện CẢNH BÁO đỏ: không ghi lại khoản thủ quỹ đã xác nhận (tránh trừ 2 lần); màn chỉ dành cho KTTH</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr"/>
+      <c r="I19" s="13" t="inlineStr"/>
+      <c r="J19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>TC-N19</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>In phiếu</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Mua hàng</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>In phiếu yêu cầu TT</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Có khoản đã nghiệm thu</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Chọn 1 phiếu → Tạo phiếu YCTT → nhập số hóa đơn → Tạo &amp; tải</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Tải được file Excel (KHÔNG còn lỗi); phiếu có đủ nhãn: Yêu cầu bởi, Bộ phận, Mục đích, Người hưởng, Tài khoản, Tại Ngân hàng</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr"/>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>Lỗi cũ do comment VML đã sửa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>TC-N20</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Phân quyền</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Tài khoản</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Tạo tài khoản vai trò "Thủ quỹ" + gán Bộ phận cho các tài khoản</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Tạo/sửa được vai trò Thủ quỹ; lưu bộ phận thành công</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr"/>
+      <c r="I21" s="13" t="inlineStr"/>
+      <c r="J21" s="13" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>TC-N21</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Theo dõi ĐXMH</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Kế toán</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Theo dõi đề xuất mua hàng &amp; tạm ứng</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Có phiếu nhiều trạng thái + phiếu nháp</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Lọc theo Trạng thái (Chờ duyệt/Đã duyệt) + khoảng ngày; click 1 phiếu quá khứ</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Lọc đúng; KHÔNG hiện phiếu Nháp chưa trình; click phiếu (kể cả cũ) xem đủ thông tin</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr"/>
+      <c r="J22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>TC-N22</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Thông báo</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Mọi vai trò</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Chuông thông báo</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Có phát sinh</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Xem nội dung thông báo ĐXMH/ĐXTT/duyệt hồ sơ</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Ghi rõ mặt hàng/nội dung + TỔNG TIỀN + người đề nghị/lập (không chỉ mã phiếu)</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>TC-N23</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Kỹ thuật</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>Supabase Storage bucket "attachments"</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Đã upload ở các bước trên</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>Mở Storage, xem đường dẫn file</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>File nằm đúng nhánh nghiệp vụ: bao-gia/ · nghiem-thu/vat/ · nghiem-thu/chung-tu/ · chi-tien/uy-nhiem/ · chat/</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr"/>
+      <c r="I24" s="13" t="inlineStr"/>
+      <c r="J24" s="13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>